--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0003T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0003T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>89.93370911917594</v>
+        <v>14.61422773186609</v>
       </c>
       <c r="D2" t="n">
-        <v>87.22783891821111</v>
+        <v>14.17452382420931</v>
       </c>
       <c r="E2" t="n">
-        <v>27.956106408986</v>
+        <v>4.542867291460225</v>
       </c>
       <c r="F2" t="n">
-        <v>31.99454618167731</v>
+        <v>5.199113754522563</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.07929315596547</v>
+        <v>3.587885137844389</v>
       </c>
       <c r="D3" t="n">
-        <v>17.04747774258147</v>
+        <v>2.770215133169489</v>
       </c>
       <c r="E3" t="n">
-        <v>27.956106408986</v>
+        <v>4.542867291460225</v>
       </c>
       <c r="F3" t="n">
-        <v>31.99454618167731</v>
+        <v>5.199113754522563</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.02019030614342</v>
+        <v>7.803280924748306</v>
       </c>
       <c r="D4" t="n">
-        <v>21.93058774890326</v>
+        <v>3.563720509196779</v>
       </c>
       <c r="E4" t="n">
-        <v>27.956106408986</v>
+        <v>4.542867291460225</v>
       </c>
       <c r="F4" t="n">
-        <v>31.99454618167731</v>
+        <v>5.199113754522563</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
